--- a/source/relatorios/producoes.xlsx
+++ b/source/relatorios/producoes.xlsx
@@ -139,7 +139,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.15"/>
   </cols>
@@ -160,10 +160,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -174,7 +174,7 @@
         <v>51</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -193,10 +193,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
